--- a/public/downloads/truecap-rental-property-analyzer.xlsx
+++ b/public/downloads/truecap-rental-property-analyzer.xlsx
@@ -1088,7 +1088,7 @@
         <x:v>Net Operating Income ÷ property value. The unleveraged return a property generates, independent of financing.</x:v>
       </x:c>
       <x:c r="C5" t="str">
-        <x:v>Typical: 5–6% in Tier-1 coastal, 6–8% Midwest / Sun Belt, 8–10% cash-flow markets.</x:v>
+        <x:v>No universal range is a property fact or investment threshold. Compare consistently calculated cap rates using dated, local evidence and the same expense conventions.</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -1099,7 +1099,7 @@
         <x:v>Annual cash flow ÷ total cash invested (down payment + closing + rehab). Tells you how hard your money is working.</x:v>
       </x:c>
       <x:c r="C6" t="str">
-        <x:v>Most buy-and-hold investors target 8–12%.</x:v>
+        <x:v>There is no universal target. Set a criterion that fits the strategy, financing, liquidity, and risk constraints, then verify every cash-flow and cash-invested input.</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -1177,7 +1177,7 @@
         <x:v>Property Tax</x:v>
       </x:c>
       <x:c r="B15" t="str">
-        <x:v>Annual property tax as a percent of value. Defaults to your state's effective rate (1.49% PA, 1.68% TX, etc.) — adjust for your county.</x:v>
+        <x:v>Annual property tax as a percent of value. This workbook starts at 1.1% of price as a placeholder; replace it with the local annual bill or a reviewed local effective rate.</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -1201,7 +1201,7 @@
         <x:v>Down Payment %</x:v>
       </x:c>
       <x:c r="B18" t="str">
-        <x:v>Share of the purchase price you pay in cash. Investment-property lenders typically require 20-25% down for conventional loans.</x:v>
+        <x:v>Share of the purchase price you pay in cash. Required investment-property down payment varies by occupancy, borrower, property, lender, and loan program.</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
